--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137305402</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137305278</v>
       </c>
       <c r="B3" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>137305344</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137305360</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>137305391</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137305254</v>
+        <v>137336648</v>
       </c>
       <c r="B7" t="n">
-        <v>93491</v>
+        <v>93468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,37 +1222,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bogöl, Sm</t>
+          <t>Bogölen öst, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572601</v>
+        <v>572514</v>
       </c>
       <c r="R7" t="n">
-        <v>6452641</v>
+        <v>6452636</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,7 +1275,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Hannäs</t>
+          <t>Gärdserum</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1293,63 +1294,60 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305254</t>
+          <t>https://artportalen.se/Sighting/137336648</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137305415</v>
+        <v>137305254</v>
       </c>
       <c r="B8" t="n">
-        <v>8470</v>
+        <v>93492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572428</v>
+        <v>572601</v>
       </c>
       <c r="R8" t="n">
-        <v>6452783</v>
+        <v>6452641</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1380,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Gärdserum</t>
+          <t>Hannäs</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1419,58 +1417,62 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305415</t>
+          <t>https://artportalen.se/Sighting/137305254</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137305352</v>
+        <v>137336646</v>
       </c>
       <c r="B9" t="n">
-        <v>106556</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bogöl, Sm</t>
+          <t>Bogölen öst, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572528</v>
+        <v>572514</v>
       </c>
       <c r="R9" t="n">
-        <v>6452709</v>
+        <v>6452785</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1508,25 +1510,773 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137336646</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137336647</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bogölen öst, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572497</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6452778</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137336647</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137336643</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58189</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bogölen öst, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>572515</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6452687</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137336643</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137336645</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58189</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bogölen öst, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>572514</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6452785</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137336645</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137305415</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bogöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>572428</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6452783</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137305415</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137336650</v>
+      </c>
+      <c r="B14" t="n">
+        <v>111399</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bogölen öst, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>572602</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6452624</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137336650</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137305352</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106557</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bogöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>572528</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6452709</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137305352</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137336654</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101620</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bogölen öst, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572591</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6452631</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137336654</t>
         </is>
       </c>
     </row>
@@ -1540,6 +2290,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305402</v>
       </c>
       <c r="B2" t="n">
-        <v>92795</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137305278</v>
       </c>
       <c r="B3" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>137305344</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137305360</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>137305391</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137336648</v>
       </c>
       <c r="B7" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137305254</v>
       </c>
       <c r="B8" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>137336646</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137336647</v>
       </c>
       <c r="B10" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137336643</v>
       </c>
       <c r="B11" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>137336645</v>
       </c>
       <c r="B12" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>137336650</v>
       </c>
       <c r="B14" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137305352</v>
       </c>
       <c r="B15" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>137336654</v>
       </c>
       <c r="B16" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305402</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137305278</v>
       </c>
       <c r="B3" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>137305344</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137305360</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>137305391</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137336648</v>
       </c>
       <c r="B7" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137305254</v>
       </c>
       <c r="B8" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>137336650</v>
       </c>
       <c r="B14" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137305352</v>
       </c>
       <c r="B15" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>137336654</v>
       </c>
       <c r="B16" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305402</v>
       </c>
       <c r="B2" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137305278</v>
       </c>
       <c r="B3" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>137305344</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137305360</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>137305391</v>
       </c>
       <c r="B6" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137336648</v>
       </c>
       <c r="B7" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137305254</v>
       </c>
       <c r="B8" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>137336646</v>
       </c>
       <c r="B9" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137336647</v>
       </c>
       <c r="B10" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137336643</v>
       </c>
       <c r="B11" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>137336645</v>
       </c>
       <c r="B12" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>137336650</v>
       </c>
       <c r="B14" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137305352</v>
       </c>
       <c r="B15" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>137336654</v>
       </c>
       <c r="B16" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -1974,7 +1974,7 @@
         <v>137336650</v>
       </c>
       <c r="B14" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137305352</v>
       </c>
       <c r="B15" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305402</v>
       </c>
       <c r="B2" t="n">
-        <v>92805</v>
+        <v>92817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137305278</v>
       </c>
       <c r="B3" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>137305344</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137305360</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>137305391</v>
       </c>
       <c r="B6" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137336648</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137305254</v>
       </c>
       <c r="B8" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>137336650</v>
       </c>
       <c r="B14" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137305352</v>
       </c>
       <c r="B15" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>137336654</v>
       </c>
       <c r="B16" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305402</v>
       </c>
       <c r="B2" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137305278</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>137305344</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137305360</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>137305391</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137336648</v>
       </c>
       <c r="B7" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137305254</v>
       </c>
       <c r="B8" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>137336650</v>
       </c>
       <c r="B14" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137305352</v>
       </c>
       <c r="B15" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>137336654</v>
       </c>
       <c r="B16" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305402</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137305278</v>
       </c>
       <c r="B3" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>137305344</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137305360</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>137305391</v>
       </c>
       <c r="B6" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137336648</v>
       </c>
       <c r="B7" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137305254</v>
       </c>
       <c r="B8" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>137336650</v>
       </c>
       <c r="B14" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137305352</v>
       </c>
       <c r="B15" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>137336654</v>
       </c>
       <c r="B16" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40918-2026 artfynd.xlsx
+++ b/artfynd/A 40918-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305402</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137305278</v>
       </c>
       <c r="B3" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>137305344</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137305360</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>137305391</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137336648</v>
       </c>
       <c r="B7" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137305254</v>
       </c>
       <c r="B8" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>137336646</v>
       </c>
       <c r="B9" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137336647</v>
       </c>
       <c r="B10" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137336643</v>
       </c>
       <c r="B11" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>137336645</v>
       </c>
       <c r="B12" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>137336650</v>
       </c>
       <c r="B14" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>137305352</v>
       </c>
       <c r="B15" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>137336654</v>
       </c>
       <c r="B16" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
